--- a/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
+++ b/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -724,71 +724,71 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Апелляционное определение Омского облсуда от 12.11.2014 № 33-7199/14</t>
+          <t>Иск семьи погибшего к ООО «Новый мир» (гибель 03.08.2013; решение Ворошиловского райсуда г. Ростова-на-Дону от 18.07.2014; 4 КСОЮ 2024)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Омский областной суд</t>
+          <t>Ворошиловский райсуд г. Ростова-на-Дону → 4 КСОЮ</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>НС: нет подписи в журнале → моральный вред</t>
+          <t>НС: подделка подписей в журналах инструктажа</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Да — НС</t>
+          <t>Да — смертельный НС</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Травма токаря при работе со станком (стаж ~14 лет); отметки об инструктаже в журнале нет</t>
+          <t>Гибель сварщика на стройке; в акте НС — допуск без вводного/первичного инструктажа и стажировки</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Подписи/записи в журнале отсутствуют</t>
+          <t>Подписи погибшего в журнале вводного инструктажа, журнале первичного инструктажа и протоколе проверки знаний — подделаны для сокрытия обстоятельств гибели</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Работодатель ссылался на неосторожность работника и стаж</t>
+          <t>Компенсация морального вреда семье; причина НС — непроведение инструктажей</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>За работника: компенсация морального вреда</t>
+          <t>Суды признали фальсификацию подписей и нарушения ОТ; длительный спор о размере компенсации (кассация 2024)</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Работник / семья</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>Нет записи в журнале при НС = работодатель не доказал инструктаж</t>
+          <t>Классика: после смертельного НС «нарисовали» подписи в журналах инструктажа</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>НС: нет подписи/обучения</t>
+          <t>НС: подделка подписи в журнале</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>https://t-j.ru/news/rostrud-sam-sebe/</t>
+          <t>https://4kas.sudrf.ru/modules.php?case_type=0&amp;delo_id=2800001&amp;name=sud_delo&amp;name_op=doc&amp;new=2800001&amp;number=33783561&amp;srv_num=1&amp;text_number=1</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>НС-подборка</t>
+          <t>Доп. НС-подборка</t>
         </is>
       </c>
     </row>
@@ -797,71 +797,71 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Решение Ханты-Мансийского райсуда от 11.07.2016 № 12-460/2016</t>
+          <t>Апелляционное определение Омского облсуда от 12.11.2014 № 33-7199/14</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский районный суд</t>
+          <t>Омский областной суд</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Особые категории работников</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>НС: нет подписи в журнале → моральный вред</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Да — НС</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Штраф за непроведение инструктажей дистанционным работникам</t>
+          <t>Травма токаря при работе со станком (стаж ~14 лет); отметки об инструктаже в журнале нет</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Подписей в журнале нет (инструктажи не проводились)</t>
+          <t>Подписи/записи в журнале отсутствуют</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Распространяются ли требования об инструктаже на дистанционных</t>
+          <t>Работодатель ссылался на неосторожность работника и стаж</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Работодатель выиграл (состав правонарушения отсутствует)</t>
+          <t>За работника: компенсация морального вреда</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>Работодатель</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Для дистанционщиков тогда иной режим (с оговоркой по ЛНА)</t>
+          <t>Нет записи в журнале при НС = работодатель не доказал инструктаж</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Дистанционные vs обычные работники</t>
+          <t>НС: нет подписи/обучения</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://e.tspor.ru/822426</t>
+          <t>https://t-j.ru/news/rostrud-sam-sebe/</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Общая практика</t>
+          <t>НС-подборка</t>
         </is>
       </c>
     </row>
@@ -870,66 +870,66 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Постановление ВС РФ от 01.03.2017 № 84-АД17-1</t>
+          <t>Решение Ханты-Мансийского райсуда от 11.07.2016 № 12-460/2016</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Верховный Суд РФ</t>
+          <t>Ханты-Мансийский районный суд</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Инструктаж / обучение не проводились</t>
+          <t>Особые категории работников</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Нет (админ)</t>
+          <t>Нет</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Не проводятся вводные/первичные/повторные инструктажи; нет сведений об ознакомлении с инструкциями по ОТ</t>
+          <t>Штраф за непроведение инструктажей дистанционным работникам</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Подписей/записей фактически нет</t>
+          <t>Подписей в журнале нет (инструктажи не проводились)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Системное отсутствие инструктажей и обучения</t>
+          <t>Распространяются ли требования об инструктаже на дистанционных</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Работодатель проиграл</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>ГИТ</t>
+          <t>Работодатель выиграл (состав правонарушения отсутствует)</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Работодатель</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Крайний случай «нет подписи, потому что не было инструктажа»</t>
+          <t>Для дистанционщиков тогда иной режим (с оговоркой по ЛНА)</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Отсутствие инструктажа</t>
+          <t>Дистанционные vs обычные работники</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-01032017-n-84-ad17-1/</t>
+          <t>https://e.tspor.ru/822426</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Постановление ВС РФ от 03.07.2017 № 83-АД17-2</t>
+          <t>Постановление ВС РФ от 01.03.2017 № 84-АД17-1</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -957,27 +957,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Формальность дат / документов</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Косвенно (логика формальности применяется и при НС)</t>
+          <t>Инструктаж / обучение не проводились</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Нет (админ)</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Подпись/документы об обучении есть, но в указанные даты работник был в командировке</t>
+          <t>Не проводятся вводные/первичные/повторные инструктажи; нет сведений об ознакомлении с инструкциями по ОТ</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Даты в документах не совпадают с фактической возможностью пройти обучение</t>
+          <t>Подписей/записей фактически нет</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Формальное обучение по ОТ; допуск без реального обучения/проверки знаний</t>
+          <t>Системное отсутствие инструктажей и обучения</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -987,27 +987,27 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>ГИТ / государство</t>
+          <t>ГИТ</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Наличие журнала/удостоверения не спасает, если даты нереальны. «Подпись есть» ≠ «инструктаж был».</t>
+          <t>Крайний случай «нет подписи, потому что не было инструктажа»</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Формальность vs реальность</t>
+          <t>Отсутствие инструктажа</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-03072017-n-83-ad17-2/</t>
+          <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-01032017-n-84-ad17-1/</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС-логика</t>
+          <t>Общая практика</t>
         </is>
       </c>
     </row>
@@ -1016,71 +1016,71 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Решение Советского райсуда г. Владивостока от 02.04.2019 № 12-183/19</t>
+          <t>Постановление ВС РФ от 03.07.2017 № 83-АД17-2</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Советский райсуд г. Владивостока</t>
+          <t>Верховный Суд РФ</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Инструктаж после приёма / с опозданием</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Нет (админштраф)</t>
+          <t>Формальность дат / документов</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Косвенно (логика формальности применяется и при НС)</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>ПАО «Дальприбор»: первичный инструктаж — фамилии нет в журнале / запись спустя ~11 дней после приказа</t>
+          <t>Подпись/документы об обучении есть, но в указанные даты работник был в командировке</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Запись в журнале ПОСЛЕ приёма, с разрывом дат; копии журнала расходятся</t>
+          <t>Даты в документах не совпадают с фактической возможностью пройти обучение</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Допуск к работе без своевременного инструктажа/обучения (ч. 3 ст. 5.27.1 КоАП)</t>
+          <t>Формальное обучение по ОТ; допуск без реального обучения/проверки знаний</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Работодатель (должностное лицо) проиграл по сути нарушения</t>
+          <t>Работодатель проиграл</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>ГИТ</t>
+          <t>ГИТ / государство</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>Поздняя запись / расхождение журналов = сильный аргумент против работодателя</t>
+          <t>Наличие журнала/удостоверения не спасает, если даты нереальны. «Подпись есть» ≠ «инструктаж был».</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Опоздание инструктажа после приёма</t>
+          <t>Формальность vs реальность</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>https://sttkrf.ru/reshenie-12-18319-ot-02-04-2019-sovetskogo-rajonnogo-suda-g-vladivostoka-primorskij-kraj</t>
+          <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-03072017-n-83-ad17-2/</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Общая практика</t>
+          <t>Общая + НС-логика</t>
         </is>
       </c>
     </row>
@@ -1093,67 +1093,67 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Спор родственников погибшего vs металлургическое предприятие (в публикации — «Глазковы» / ООО «Евразия», фамилии изменены)</t>
+          <t>Дело Ермолаева С.И. vs ООО «Чулымский хлебозавод» (определение ВС РФ 04.07.2022 № 67-КГ22-6-К8)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Суд общей юрисдикции + экспертиза в уголовном деле</t>
+          <t>Чулымский городской суд → ВС РФ</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>НС: спор о подлинности подписи после гибели</t>
+          <t>НС: не проходил инструктаж → моральный вред</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Да — смертельный НС</t>
+          <t>Да — НС</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Гибель ремонтника; спор о подписи в личной карточке на внеплановый инструктаж (дата исправлялась)</t>
+          <t>Падение со стремянки 10.01.2019 при работе в гараже; работодатель скрыл НС, не оформил акт Н-1</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Две почерковедческие экспертизы + рецензия; выводы противоречивы</t>
+          <t>Инструктаж по технике безопасности не проводился; записей/подписей нет</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Был ли реальный внеплановый инструктаж до НС</t>
+          <t>Установление факта НС и взыскание морального вреда</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Спорный/процессуальный: исход зависит от повторной экспертизы</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Смешанный</t>
+          <t>За работника: НС признан, 80 000 ₽ морального вреда (из запрошенных 500 000 ₽)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Работник</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>После смертельного НС подпись в карточке инструктажа — центральное доказательство</t>
+          <t>Отсутствие инструктажа + сокрытие НС усиливают позицию работника</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>НС: подделка / подлинность подписи</t>
+          <t>НС: нет подписи/обучения</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>https://recense.exprus.ru/protivorechivye-itogi/</t>
+          <t>https://legalacts.ru/sud/opredelenie-sudebnoi-kollegii-po-grazhdanskim-delam-verkhovnogo-suda-rossiiskoi-federatsii-ot-04072022-n-67-kg22-6-k8/</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>НС-подборка</t>
+          <t>Доп. НС-подборка</t>
         </is>
       </c>
     </row>
@@ -1162,16 +1162,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Постановление 6 КСОЮ от 08.05.2020 № 16-3241/2020</t>
+          <t>Решение Советского райсуда г. Владивостока от 02.04.2019 № 12-183/19</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Шестой кассационный СОЮ</t>
+          <t>Советский райсуд г. Владивостока</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1181,27 +1181,27 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Нет (админ / давность)</t>
+          <t>Нет (админштраф)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Спор о сроке давности: когда начинается ответственность за допуск без обучения</t>
+          <t>ПАО «Дальприбор»: первичный инструктаж — фамилии нет в журнале / запись спустя ~11 дней после приказа</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Допуск без обучения/проверки знаний</t>
+          <t>Запись в журнале ПОСЛЕ приёма, с разрывом дат; копии журнала расходятся</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>ч. 3 ст. 5.27.1 КоАП — за допуск без обучения, а не только за пропуск срока обучения</t>
+          <t>Допуск к работе без своевременного инструктажа/обучения (ч. 3 ст. 5.27.1 КоАП)</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Позиция ужесточена для работодателя (давность от допуска)</t>
+          <t>Работодатель (должностное лицо) проиграл по сути нарушения</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Критичен факт допуска без обучения</t>
+          <t>Поздняя запись / расхождение журналов = сильный аргумент против работодателя</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>https://www.kiout.ru/info/news/29653</t>
+          <t>https://sttkrf.ru/reshenie-12-18319-ot-02-04-2019-sovetskogo-rajonnogo-suda-g-vladivostoka-primorskij-kraj</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
@@ -1235,66 +1235,66 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Апелляция Ульяновского облсуда (дело Хасанова Д.Р. — отказ в моральном вреде при НС)</t>
+          <t>Спор родственников погибшего vs металлургическое предприятие (в публикации — «Глазковы» / ООО «Евразия», фамилии изменены)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Ульяновский областной суд</t>
+          <t>Суд общей юрисдикции + экспертиза в уголовном деле</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>НС: подписи в журнале есть → вина работника</t>
+          <t>НС: спор о подлинности подписи после гибели</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Да — НС</t>
+          <t>Да — смертельный НС</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>НС плавильщика; иск о моральном вреде; есть выписки из журналов вводного и повторного инструктажа</t>
+          <t>Гибель ремонтника; спор о подписи в личной карточке на внеплановый инструктаж (дата исправлялась)</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Подписи/записи в журналах подтверждены</t>
+          <t>Две почерковедческие экспертизы + рецензия; выводы противоречивы</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Работодатель доказал инструктажи и меры ОТ; причина — неосторожность работника</t>
+          <t>Был ли реальный внеплановый инструктаж до НС</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>За работодателя: отказ во взыскании морального вреда</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Работодатель</t>
+          <t>Спорный/процессуальный: исход зависит от повторной экспертизы</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Смешанный</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Противоположность к делам без журнала: подтверждённые подписи защищают работодателя</t>
+          <t>После смертельного НС подпись в карточке инструктажа — центральное доказательство</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>НС: подпись есть vs нет</t>
+          <t>НС: подделка / подлинность подписи</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>http://www.uloblsud.ru/index.php?id=90&amp;idCard=91321&amp;option=3</t>
+          <t>https://recense.exprus.ru/protivorechivye-itogi/</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -1308,46 +1308,46 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Апелляционное определение Архангельского облсуда от 04.09.2024 № 33а-6948/2024</t>
+          <t>Постановление 6 КСОЮ от 08.05.2020 № 16-3241/2020</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Архангельский областной суд</t>
+          <t>Шестой кассационный СОЮ</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>НС: нет обучения/инструктажа как причина</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Да — НС</t>
+          <t>Инструктаж после приёма / с опозданием</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Нет (админ / давность)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Оператор станка допущен через неделю после найма без обучения, проверки знаний и стажировки (≥2 смены); НС (лёгкий вред)</t>
+          <t>Спор о сроке давности: когда начинается ответственность за допуск без обучения</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Допуск к работе без своевременного обучения/инструктажа после приёма</t>
+          <t>Допуск без обучения/проверки знаний</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Работодатель указал вину работника; ГИТ — причина НС в недостаточной подготовке по ОТ</t>
+          <t>ч. 3 ст. 5.27.1 КоАП — за допуск без обучения, а не только за пропуск срока обучения</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Против работодателя: акт Н-1 должен отражать подготовку/обучение как причину НС</t>
+          <t>Позиция ужесточена для работодателя (давность от допуска)</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -1357,22 +1357,22 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Отсутствие оформленного инструктажа/обучения признано причиной НС</t>
+          <t>Критичен факт допуска без обучения</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>НС: нет подписи/обучения</t>
+          <t>Опоздание инструктажа после приёма</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>https://www.garant.ru/news/1761291/</t>
+          <t>https://www.kiout.ru/info/news/29653</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Общая практика</t>
         </is>
       </c>
     </row>
@@ -1381,71 +1381,71 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Разъяснение Онлайнинспекция.рф / Роструд (позиция надзора, не судебный акт)</t>
+          <t>Апелляция Ульяновского облсуда (дело Хасанова Д.Р. — отказ в моральном вреде при НС)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Роструд (Онлайнинспекция.рф)</t>
+          <t>Ульяновский областной суд</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Инструктаж до ТД / приёма</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>НС: подписи в журнале есть → вина работника</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Да — НС</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Можно ли провести вводный инструктаж / обучение до приёма</t>
+          <t>НС плавильщика; иск о моральном вреде; есть выписки из журналов вводного и повторного инструктажа</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>До заключения ТД — нельзя (позиция надзора)</t>
+          <t>Подписи/записи в журналах подтверждены</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Инструктаж проводят с работником, а не с соискателем</t>
+          <t>Работодатель доказал инструктажи и меры ОТ; причина — неосторожность работника</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Позиция: инструктаж до ТД недопустим</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>Надзор (против раннего инструктажа)</t>
+          <t>За работодателя: отказ во взыскании морального вреда</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Работодатель</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Противоположность к 08АП-10045/25: надзор формально строже суда</t>
+          <t>Противоположность к делам без журнала: подтверждённые подписи защищают работодателя</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>До ТД: суд vs разъяснения Роструда</t>
+          <t>НС: подпись есть vs нет</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>https://trud-eao.ru/?p=4530</t>
+          <t>http://www.uloblsud.ru/index.php?id=90&amp;idCard=91321&amp;option=3</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Общая практика (разъяснение)</t>
+          <t>НС-подборка</t>
         </is>
       </c>
     </row>
@@ -1454,71 +1454,71 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Дело № 2-357/2025 (Железнодорожный райсуд г. Красноярска)</t>
+          <t>Уголовное дело ООО «Зерновая компания» (Элиста, гибель грузчика 30.06.2023, ст. 143 УК РФ)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Железнодорожный райсуд г. Красноярска</t>
+          <t>Следствие / суд (уголовное дело; по публикациям специалистов по ОТ)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>НС: анализ журнала/карточки</t>
+          <t>НС: подписи в журналах задним числом после гибели</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Да — НС (контекст)</t>
+          <t>Да — смертельный НС</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>В материалах проверяются записи о вводном/первичном инструктаже, стажировке, обучении водителя-экспедитора</t>
+          <t>Грузчик спустился в бункер без наряда-допуска; засыпало зерном</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Суд анализирует, были ли инструктажи до допуска</t>
+          <t>Вводный и первичный инструктажи не проводились; подписи в журналах проставлены задним числом после гибели</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Связь инструктажа/обучения с допуском и обстоятельствами НС/спора</t>
+          <t>Уголовная ответственность инженера по ОТ (приказом на него возложены процедуры допуска)</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>См. полный текст решения (анализ документов ОТ)</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>Смешанный / зависит от установленных фактов</t>
+          <t>Уголовное дело; прекращено с примирением (выплата семье 1 млн ₽)</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>ГИТ / следствие против должностных лиц</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>Журнал инструктажа — ключевое доказательство при НС</t>
+          <t>Подпись «задним числом» после смертельного НС — уголовно значимая фальсификация</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>НС и журнал инструктажа</t>
+          <t>НС: подделка подписи в журнале</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>https://geldor--krk.sudrf.ru/modules.php?delo_id=1540005&amp;name=sud_delo&amp;name_op=doc&amp;new=&amp;number=498763687&amp;text_number=1</t>
+          <t>https://e.otruda.ru/1185487</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Доп. НС-подборка (обзор)</t>
         </is>
       </c>
     </row>
@@ -1527,46 +1527,46 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Постановление 9 КСОЮ от 18.07.2025 № 16-1837/2025</t>
+          <t>Апелляционное определение Архангельского облсуда от 04.09.2024 № 33а-6948/2024</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Девятый кассационный СОЮ</t>
+          <t>Архангельский областной суд</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Ошибки оформления журнала</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
+          <t>НС: нет обучения/инструктажа как причина</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Да — НС</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>В журнале инструктажей отсутствуют обязательные реквизиты (дата рождения, наименование ЛНА и т.п.)</t>
+          <t>Оператор станка допущен через неделю после найма без обучения, проверки знаний и стажировки (≥2 смены); НС (лёгкий вред)</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Запись/подпись есть, но оформление неполное</t>
+          <t>Допуск к работе без своевременного обучения/инструктажа после приёма</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Нарушение порядка регистрации инструктажа</t>
+          <t>Работодатель указал вину работника; ГИТ — причина НС в недостаточной подготовке по ОТ</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Работодатель проиграл (штраф/ответственность подтверждены)</t>
+          <t>Против работодателя: акт Н-1 должен отражать подготовку/обучение как причину НС</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
@@ -1576,22 +1576,22 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>Даже при факте инструктажа кривое оформление журнала = риск</t>
+          <t>Отсутствие оформленного инструктажа/обучения признано причиной НС</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Оформление журнала</t>
+          <t>НС: нет подписи/обучения</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>https://1c-prime.ru/articles/rekomendatsii-novye-stati-2025/shtrafy-za-oshibki-v-zhurnale-instruktazhey-po-okhrane-truda-kak-izbezhat-nakazaniya-do-150-000-/</t>
+          <t>https://www.garant.ru/news/1761291/</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Общая практика</t>
+          <t>Общая + НС</t>
         </is>
       </c>
     </row>
@@ -1600,71 +1600,71 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Решение Московского райсуда г. Н. Новгорода № 2-17/2025 (UID 52RS0004-01-2024-000600-19)</t>
+          <t>Разъяснение Онлайнинспекция.рф / Роструд (позиция надзора, не судебный акт)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Московский райсуд г. Нижнего Новгорода</t>
+          <t>Роструд (Онлайнинспекция.рф)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>НС: подделка подписи в карточке инструктажа</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Да — НС</t>
+          <t>Инструктаж до ТД / приёма</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Тяжёлая травма слесаря ПАО «ОАК»; в акте Н-1 вменили нарушение ИОТ; экспертиза: подписи в карточке инструктажа — чужие</t>
+          <t>Можно ли провести вводный инструктаж / обучение до приёма</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Подпись в карточке — не работника (фальсификация после/для спора о НС)</t>
+          <t>До заключения ТД — нельзя (позиция надзора)</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Фальсификация фиксации инструктажа для возложения вины на работника</t>
+          <t>Инструктаж проводят с работником, а не с соискателем</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>За работника: ~1,3 млн ₽ морального вреда; акт Н-1 частично отменён</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Работник</t>
+          <t>Позиция: инструктаж до ТД недопустим</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Надзор (против раннего инструктажа)</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>Поддельная подпись → нет надлежащего инструктажа → вина работника в НС отсутствует</t>
+          <t>Противоположность к 08АП-10045/25: надзор формально строже суда</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>НС: подделка подписи</t>
+          <t>До ТД: суд vs разъяснения Роструда</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>https://jurisdikciya.ru/delo/52RS0004-01-2024-000600-19/</t>
+          <t>https://trud-eao.ru/?p=4530</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Общая практика (разъяснение)</t>
         </is>
       </c>
     </row>
@@ -1673,69 +1673,288 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Дело № 2-357/2025 (Железнодорожный райсуд г. Красноярска)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Железнодорожный райсуд г. Красноярска</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>НС: анализ журнала/карточки</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Да — НС (контекст)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>В материалах проверяются записи о вводном/первичном инструктаже, стажировке, обучении водителя-экспедитора</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Суд анализирует, были ли инструктажи до допуска</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Связь инструктажа/обучения с допуском и обстоятельствами НС/спора</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>См. полный текст решения (анализ документов ОТ)</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Смешанный / зависит от установленных фактов</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Журнал инструктажа — ключевое доказательство при НС</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>НС и журнал инструктажа</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>https://geldor--krk.sudrf.ru/modules.php?delo_id=1540005&amp;name=sud_delo&amp;name_op=doc&amp;new=&amp;number=498763687&amp;text_number=1</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Общая + НС</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="72" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Постановление 9 КСОЮ от 18.07.2025 № 16-1837/2025</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Девятый кассационный СОЮ</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Ошибки оформления журнала</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>В журнале инструктажей отсутствуют обязательные реквизиты (дата рождения, наименование ЛНА и т.п.)</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Запись/подпись есть, но оформление неполное</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Нарушение порядка регистрации инструктажа</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Работодатель проиграл (штраф/ответственность подтверждены)</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>ГИТ</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Даже при факте инструктажа кривое оформление журнала = риск</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Оформление журнала</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>https://1c-prime.ru/articles/rekomendatsii-novye-stati-2025/shtrafy-za-oshibki-v-zhurnale-instruktazhey-po-okhrane-truda-kak-izbezhat-nakazaniya-do-150-000-/</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Общая практика</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="72" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Решение Московского райсуда г. Н. Новгорода № 2-17/2025 (UID 52RS0004-01-2024-000600-19)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Московский райсуд г. Нижнего Новгорода</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>НС: подделка подписи в карточке инструктажа</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Да — НС</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Тяжёлая травма слесаря ПАО «ОАК»; в акте Н-1 вменили нарушение ИОТ; экспертиза: подписи в карточке инструктажа — чужие</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Подпись в карточке — не работника (фальсификация после/для спора о НС)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Фальсификация фиксации инструктажа для возложения вины на работника</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>За работника: ~1,3 млн ₽ морального вреда; акт Н-1 частично отменён</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Поддельная подпись → нет надлежащего инструктажа → вина работника в НС отсутствует</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>НС: подделка подписи</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>https://jurisdikciya.ru/delo/52RS0004-01-2024-000600-19/</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Общая + НС</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="72" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="n">
         <v>2026</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Постановление 8 ААС от 23.04.2026 № 08АП-10045/25</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>8 арбитражный апелляционный суд</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Инструктаж до ТД / приёма</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Вводный и первичный инструктажи за несколько дней до заключения ТД</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Подпись/инструктаж ДО трудового договора, но ДО допуска к работе</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Прокуратура: инструктаж только для работников; на момент инструктажа лицо ещё не работник</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Работодатель выиграл (представление частично отменено)</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Работодатель</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Ранний инструктаж допустим, если до допуска и претензий к качеству нет</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>До ТД: суд vs разъяснения Роструда</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>https://www.garant.ru/news/2087655/</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
@@ -1752,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1900,79 +2119,106 @@
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Формальность документов</t>
+          <t>НС: подписи «задним числом» vs экспертиза подделки</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Журнал/карточка существуют, но не подтверждают реальное обучение</t>
+          <t>После смертельного НС в журналах появляются подписи об инструктаже</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>83-АД17-2 → нереальные даты</t>
+          <t>ООО «Зерновая компания» (2023) → подписи задним числом → уголовное дело</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>16-1837/2025 → неполные реквизиты журнала</t>
+          <t>ООО «Новый мир» (2013) / 2-17/2025 → подделка доказана судом/экспертизой</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Подпись/запись сама по себе недостаточна.</t>
+          <t>Одинаковый мотив сокрытия; разница — доказательная база (экспертиза vs следствие).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Дистанционные vs обычные работники</t>
+          <t>Формальность документов</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Нет подписей в журнале инструктажей</t>
+          <t>Журнал/карточка существуют, но не подтверждают реальное обучение</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>12-460/2016 → для дистанционщиков штраф отменён</t>
+          <t>83-АД17-2 → нереальные даты</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>84-АД17-1 / 33-2135/2012 → для обычных / при очном ЛНА — строго</t>
+          <t>16-1837/2025 → неполные реквизиты журнала</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Одинаковый факт «нет подписи», разные исходы.</t>
+          <t>Подпись/запись сама по себе недостаточна.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>Дистанционные vs обычные работники</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Нет подписей в журнале инструктажей</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>12-460/2016 → для дистанционщиков штраф отменён</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>84-АД17-1 / 33-2135/2012 → для обычных / при очном ЛНА — строго</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Одинаковый факт «нет подписи», разные исходы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>Формальность дат vs реальность допуска</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Когда должен быть инструктаж относительно допуска</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>08АП-10045/25 → можно раньше ТД, если до допуска</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>16-3241/2020 + 12-183/19 → критичен факт допуска без обучения</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Ключевая ось: не «красивая дата», а был ли допуск без подготовки.</t>
         </is>
@@ -1989,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2057,7 +2303,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>НС: нет подписи в журнале → моральный вред</t>
+          <t>НС: подделка подписей в журналах инструктажа</t>
         </is>
       </c>
       <c r="B3" s="9" t="n">
@@ -2070,23 +2316,23 @@
         <v>0</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Инструктаж / обучение не проводились</t>
+          <t>НС: нет подписи в журнале → моральный вред</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>0</v>
@@ -2101,7 +2347,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Формальность дат / документов</t>
+          <t>Инструктаж / обучение не проводились</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -2123,11 +2369,11 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Инструктаж после приёма / с опозданием</t>
+          <t>Формальность дат / документов</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>0</v>
@@ -2139,13 +2385,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>НС: спор о подлинности подписи после гибели</t>
+          <t>НС: не проходил инструктаж → моральный вред</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -2158,38 +2404,38 @@
         <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>НС: подписи в журнале есть → вина работника</t>
+          <t>Инструктаж после приёма / с опозданием</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>НС: нет обучения/инструктажа как причина</t>
+          <t>НС: спор о подлинности подписи после гибели</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -2202,26 +2448,26 @@
         <v>0</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Инструктаж до ТД / приёма</t>
+          <t>НС: подписи в журнале есть → вина работника</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
         <v>0</v>
@@ -2233,7 +2479,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>НС: анализ журнала/карточки</t>
+          <t>НС: подписи в журналах задним числом после гибели</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -2255,14 +2501,14 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Ошибки оформления журнала</t>
+          <t>НС: нет обучения/инструктажа как причина</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>0</v>
@@ -2277,22 +2523,88 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
+          <t>Инструктаж до ТД / приёма</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>НС: анализ журнала/карточки</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Ошибки оформления журнала</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
           <t>НС: подделка подписи в карточке инструктажа</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="B16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2307,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2437,49 +2749,83 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Реквизиты журнала неполные</t>
+          <t>Подписи в журналах подделаны после смертельного НС</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Против работодателя</t>
+          <t>Вина работодателя; уголовное/гражданское преследование</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>16-1837/2025</t>
+          <t>ООО «Новый мир» 2013; «Зерновая компания» 2023</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Инструктажей нет вообще</t>
+          <t>Инструктаж не проводился, НС скрыт</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Против работодателя</t>
+          <t>Моральный вред с работодателя</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>84-АД17-1</t>
+          <t>Ермолаев / Чулымский хлебозавод</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>Реквизиты журнала неполные</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Против работодателя</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>16-1837/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Инструктажей нет вообще</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Против работодателя</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>84-АД17-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Нет подписей у дистанционных (старая практика)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Иногда за работодателя</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>12-460/2016 (оговорка: 33-2135/2012)</t>
         </is>

--- a/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
+++ b/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,13 @@
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>• Важно: сама подпись НС не вызывает; суды оценивают реальность инструктажа и подлинность подписи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>• Из файла пользователя (74b7.xlsx): обновлено 9 дел, добавлено 0 новых.</t>
         </is>
       </c>
     </row>
@@ -856,12 +863,12 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>https://t-j.ru/news/rostrud-sam-sebe/</t>
+          <t>https://meganorm.ru/mega_doc/dop1/57/statya_provodim_instruktazhi_po_okhrane_truda_zhizherina_yu/0/apellyatsionnoe_opredelenie_omskogo_oblastnogo_suda_ot_12_11.html</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>НС-подборка</t>
+          <t>НС-подборка; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1087,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС-логика</t>
+          <t>Общая + НС-логика; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1306,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>НС-подборка</t>
+          <t>НС-подборка; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1374,12 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>https://www.kiout.ru/info/news/29653</t>
+          <t>https://base.garant.ru/313712200/</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Общая практика</t>
+          <t>Общая практика; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1452,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>НС-подборка</t>
+          <t>НС-подборка; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1598,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Общая + НС; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1744,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Общая + НС; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1890,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Общая + НС</t>
+          <t>Общая + НС; файл пользователя</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1963,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>Общая практика</t>
+          <t>Общая практика; файл пользователя</t>
         </is>
       </c>
     </row>

--- a/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
+++ b/Судпрактика_подпись_инструктажа_ОБЪЕДИНЁННАЯ.xlsx
@@ -39,7 +39,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,17 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -117,9 +112,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -490,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -542,6 +534,13 @@
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>• Из файла пользователя (74b7.xlsx): обновлено 9 дел, добавлено 0 новых.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>• На листе «Судебная практика»: голубая заливка — ваши 9 дел; без цвета — дополнительная подборка агента.</t>
         </is>
       </c>
     </row>
@@ -556,24 +555,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="35" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -584,70 +584,75 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>Чьё дело</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
           <t>Год</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Номер дела / акт</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Суд</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Связь с НС</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Сценарий</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Момент подписи / даты</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Предмет спора</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Исход</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>На чьей стороне</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Практический вывод</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Группа сравнения</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Источник подборки</t>
         </is>
@@ -657,70 +662,75 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>2012</v>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Апелляционное определение Томского облсуда от 14.09.2012 № 33-2135/2012</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Томский областной суд</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Особые категории работников</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>ЛНА требует личный инструктаж; попытка провести дистанционно (по телефону) недопустима</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Формат проведения vs фиксация</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Если ЛНА требует очный инструктаж — нельзя заменить телефоном</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Против упрощённой «дистанционной» фиксации при очном ЛНА</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Строгий подход к форме инструктажа</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Дистанционность не всегда освобождает</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>Дистанционные vs обычные работники</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>https://e.tspor.ru/822426</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
@@ -730,143 +740,153 @@
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>2013</v>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Иск семьи погибшего к ООО «Новый мир» (гибель 03.08.2013; решение Ворошиловского райсуда г. Ростова-на-Дону от 18.07.2014; 4 КСОЮ 2024)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Ворошиловский райсуд г. Ростова-на-Дону → 4 КСОЮ</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>НС: подделка подписей в журналах инструктажа</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Да — смертельный НС</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Гибель сварщика на стройке; в акте НС — допуск без вводного/первичного инструктажа и стажировки</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Подписи погибшего в журнале вводного инструктажа, журнале первичного инструктажа и протоколе проверки знаний — подделаны для сокрытия обстоятельств гибели</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>Компенсация морального вреда семье; причина НС — непроведение инструктажей</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Суды признали фальсификацию подписей и нарушения ОТ; длительный спор о размере компенсации (кассация 2024)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Работник / семья</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Классика: после смертельного НС «нарисовали» подписи в журналах инструктажа</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>НС: подделка подписи в журнале</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>https://4kas.sudrf.ru/modules.php?case_type=0&amp;delo_id=2800001&amp;name=sud_delo&amp;name_op=doc&amp;new=2800001&amp;number=33783561&amp;srv_num=1&amp;text_number=1</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>Доп. НС-подборка</t>
         </is>
       </c>
     </row>
     <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Апелляционное определение Омского облсуда от 12.11.2014 № 33-7199/14</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Омский областной суд</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>НС: нет подписи в журнале → моральный вред</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Да — НС</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Травма токаря при работе со станком (стаж ~14 лет); отметки об инструктаже в журнале нет</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Подписи/записи в журнале отсутствуют</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Работодатель ссылался на неосторожность работника и стаж</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>За работника: компенсация морального вреда</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Нет записи в журнале при НС = работодатель не доказал инструктаж</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>НС: нет подписи/обучения</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>https://meganorm.ru/mega_doc/dop1/57/statya_provodim_instruktazhi_po_okhrane_truda_zhizherina_yu/0/apellyatsionnoe_opredelenie_omskogo_oblastnogo_suda_ot_12_11.html</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>НС-подборка; файл пользователя</t>
         </is>
@@ -876,70 +896,75 @@
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>2016</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Решение Ханты-Мансийского райсуда от 11.07.2016 № 12-460/2016</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Ханты-Мансийский районный суд</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Особые категории работников</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Штраф за непроведение инструктажей дистанционным работникам</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Подписей в журнале нет (инструктажи не проводились)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Распространяются ли требования об инструктаже на дистанционных</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Работодатель выиграл (состав правонарушения отсутствует)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Работодатель</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Для дистанционщиков тогда иной режим (с оговоркой по ЛНА)</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Дистанционные vs обычные работники</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>https://e.tspor.ru/822426</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
@@ -949,143 +974,153 @@
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>2017</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Постановление ВС РФ от 01.03.2017 № 84-АД17-1</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Верховный Суд РФ</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Инструктаж / обучение не проводились</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Нет (админ)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Не проводятся вводные/первичные/повторные инструктажи; нет сведений об ознакомлении с инструкциями по ОТ</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Подписей/записей фактически нет</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Системное отсутствие инструктажей и обучения</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Работодатель проиграл</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>ГИТ</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Крайний случай «нет подписи, потому что не было инструктажа»</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Отсутствие инструктажа</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-01032017-n-84-ad17-1/</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
       </c>
     </row>
     <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Постановление ВС РФ от 03.07.2017 № 83-АД17-2</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Верховный Суд РФ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Формальность дат / документов</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Косвенно (логика формальности применяется и при НС)</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Подпись/документы об обучении есть, но в указанные даты работник был в командировке</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Даты в документах не совпадают с фактической возможностью пройти обучение</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Формальное обучение по ОТ; допуск без реального обучения/проверки знаний</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Работодатель проиграл</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>ГИТ / государство</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Наличие журнала/удостоверения не спасает, если даты нереальны. «Подпись есть» ≠ «инструктаж был».</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Формальность vs реальность</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>https://legalacts.ru/sud/postanovlenie-verkhovnogo-suda-rf-ot-03072017-n-83-ad17-2/</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Общая + НС-логика; файл пользователя</t>
         </is>
@@ -1095,70 +1130,75 @@
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>2019</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Дело Ермолаева С.И. vs ООО «Чулымский хлебозавод» (определение ВС РФ 04.07.2022 № 67-КГ22-6-К8)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Чулымский городской суд → ВС РФ</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>НС: не проходил инструктаж → моральный вред</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Да — НС</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Падение со стремянки 10.01.2019 при работе в гараже; работодатель скрыл НС, не оформил акт Н-1</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Инструктаж по технике безопасности не проводился; записей/подписей нет</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Установление факта НС и взыскание морального вреда</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>За работника: НС признан, 80 000 ₽ морального вреда (из запрошенных 500 000 ₽)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>Отсутствие инструктажа + сокрытие НС усиливают позицию работника</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>НС: нет подписи/обучения</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>https://legalacts.ru/sud/opredelenie-sudebnoi-kollegii-po-grazhdanskim-delam-verkhovnogo-suda-rossiiskoi-federatsii-ot-04072022-n-67-kg22-6-k8/</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Доп. НС-подборка</t>
         </is>
@@ -1168,289 +1208,309 @@
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>2019</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Решение Советского райсуда г. Владивостока от 02.04.2019 № 12-183/19</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Советский райсуд г. Владивостока</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Инструктаж после приёма / с опозданием</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Нет (админштраф)</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>ПАО «Дальприбор»: первичный инструктаж — фамилии нет в журнале / запись спустя ~11 дней после приказа</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Запись в журнале ПОСЛЕ приёма, с разрывом дат; копии журнала расходятся</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Допуск к работе без своевременного инструктажа/обучения (ч. 3 ст. 5.27.1 КоАП)</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Работодатель (должностное лицо) проиграл по сути нарушения</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>ГИТ</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>Поздняя запись / расхождение журналов = сильный аргумент против работодателя</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>Опоздание инструктажа после приёма</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>https://sttkrf.ru/reshenie-12-18319-ot-02-04-2019-sovetskogo-rajonnogo-suda-g-vladivostoka-primorskij-kraj</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Спор родственников погибшего vs металлургическое предприятие (в публикации — «Глазковы» / ООО «Евразия», фамилии изменены)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Суд общей юрисдикции + экспертиза в уголовном деле</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>НС: спор о подлинности подписи после гибели</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Да — смертельный НС</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Гибель ремонтника; спор о подписи в личной карточке на внеплановый инструктаж (дата исправлялась)</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Две почерковедческие экспертизы + рецензия; выводы противоречивы</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Был ли реальный внеплановый инструктаж до НС</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Спорный/процессуальный: исход зависит от повторной экспертизы</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Смешанный</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>После смертельного НС подпись в карточке инструктажа — центральное доказательство</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>НС: подделка / подлинность подписи</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>https://recense.exprus.ru/protivorechivye-itogi/</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>НС-подборка; файл пользователя</t>
         </is>
       </c>
     </row>
     <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Постановление 6 КСОЮ от 08.05.2020 № 16-3241/2020</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Шестой кассационный СОЮ</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Инструктаж после приёма / с опозданием</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Нет (админ / давность)</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Спор о сроке давности: когда начинается ответственность за допуск без обучения</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Допуск без обучения/проверки знаний</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>ч. 3 ст. 5.27.1 КоАП — за допуск без обучения, а не только за пропуск срока обучения</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Позиция ужесточена для работодателя (давность от допуска)</t>
         </is>
       </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>ГИТ</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Критичен факт допуска без обучения</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Опоздание инструктажа после приёма</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>https://base.garant.ru/313712200/</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Общая практика; файл пользователя</t>
         </is>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Апелляция Ульяновского облсуда (дело Хасанова Д.Р. — отказ в моральном вреде при НС)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Ульяновский областной суд</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>НС: подписи в журнале есть → вина работника</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Да — НС</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>НС плавильщика; иск о моральном вреде; есть выписки из журналов вводного и повторного инструктажа</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Подписи/записи в журналах подтверждены</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Работодатель доказал инструктажи и меры ОТ; причина — неосторожность работника</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>За работодателя: отказ во взыскании морального вреда</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Работодатель</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Противоположность к делам без журнала: подтверждённые подписи защищают работодателя</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>НС: подпись есть vs нет</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>http://www.uloblsud.ru/index.php?id=90&amp;idCard=91321&amp;option=3</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>НС-подборка; файл пользователя</t>
         </is>
@@ -1460,143 +1520,153 @@
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>2023</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Уголовное дело ООО «Зерновая компания» (Элиста, гибель грузчика 30.06.2023, ст. 143 УК РФ)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Следствие / суд (уголовное дело; по публикациям специалистов по ОТ)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>НС: подписи в журналах задним числом после гибели</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Да — смертельный НС</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Грузчик спустился в бункер без наряда-допуска; засыпало зерном</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Вводный и первичный инструктажи не проводились; подписи в журналах проставлены задним числом после гибели</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Уголовная ответственность инженера по ОТ (приказом на него возложены процедуры допуска)</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Уголовное дело; прекращено с примирением (выплата семье 1 млн ₽)</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>ГИТ / следствие против должностных лиц</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Подпись «задним числом» после смертельного НС — уголовно значимая фальсификация</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>НС: подделка подписи в журнале</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>https://e.otruda.ru/1185487</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Доп. НС-подборка (обзор)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Апелляционное определение Архангельского облсуда от 04.09.2024 № 33а-6948/2024</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Архангельский областной суд</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>НС: нет обучения/инструктажа как причина</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Да — НС</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Оператор станка допущен через неделю после найма без обучения, проверки знаний и стажировки (≥2 смены); НС (лёгкий вред)</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Допуск к работе без своевременного обучения/инструктажа после приёма</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Работодатель указал вину работника; ГИТ — причина НС в недостаточной подготовке по ОТ</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Против работодателя: акт Н-1 должен отражать подготовку/обучение как причину НС</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>ГИТ</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Отсутствие оформленного инструктажа/обучения признано причиной НС</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>НС: нет подписи/обучения</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>https://www.garant.ru/news/1761291/</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Общая + НС; файл пользователя</t>
         </is>
@@ -1606,143 +1676,153 @@
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>2024</v>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Разъяснение Онлайнинспекция.рф / Роструд (позиция надзора, не судебный акт)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Роструд (Онлайнинспекция.рф)</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Инструктаж до ТД / приёма</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Можно ли провести вводный инструктаж / обучение до приёма</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>До заключения ТД — нельзя (позиция надзора)</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Инструктаж проводят с работником, а не с соискателем</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Позиция: инструктаж до ТД недопустим</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Надзор (против раннего инструктажа)</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>Противоположность к 08АП-10045/25: надзор формально строже суда</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>До ТД: суд vs разъяснения Роструда</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>https://trud-eao.ru/?p=4530</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>Общая практика (разъяснение)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="4" t="n">
+      <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Дело № 2-357/2025 (Железнодорожный райсуд г. Красноярска)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Железнодорожный райсуд г. Красноярска</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>НС: анализ журнала/карточки</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Да — НС (контекст)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>В материалах проверяются записи о вводном/первичном инструктаже, стажировке, обучении водителя-экспедитора</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Суд анализирует, были ли инструктажи до допуска</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Связь инструктажа/обучения с допуском и обстоятельствами НС/спора</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>См. полный текст решения (анализ документов ОТ)</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Смешанный / зависит от установленных фактов</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Журнал инструктажа — ключевое доказательство при НС</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>НС и журнал инструктажа</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>https://geldor--krk.sudrf.ru/modules.php?delo_id=1540005&amp;name=sud_delo&amp;name_op=doc&amp;new=&amp;number=498763687&amp;text_number=1</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>Общая + НС; файл пользователя</t>
         </is>
@@ -1752,216 +1832,231 @@
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Доп. подборка</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>2025</v>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Постановление 9 КСОЮ от 18.07.2025 № 16-1837/2025</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Девятый кассационный СОЮ</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Ошибки оформления журнала</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>В журнале инструктажей отсутствуют обязательные реквизиты (дата рождения, наименование ЛНА и т.п.)</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Запись/подпись есть, но оформление неполное</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>Нарушение порядка регистрации инструктажа</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Работодатель проиграл (штраф/ответственность подтверждены)</t>
         </is>
       </c>
-      <c r="K17" s="8" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>ГИТ</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Даже при факте инструктажа кривое оформление журнала = риск</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>Оформление журнала</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>https://1c-prime.ru/articles/rekomendatsii-novye-stati-2025/shtrafy-za-oshibki-v-zhurnale-instruktazhey-po-okhrane-truda-kak-izbezhat-nakazaniya-do-150-000-/</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Общая практика</t>
         </is>
       </c>
     </row>
     <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="4" t="n">
+      <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Решение Московского райсуда г. Н. Новгорода № 2-17/2025 (UID 52RS0004-01-2024-000600-19)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Московский райсуд г. Нижнего Новгорода</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>НС: подделка подписи в карточке инструктажа</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Да — НС</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Тяжёлая травма слесаря ПАО «ОАК»; в акте Н-1 вменили нарушение ИОТ; экспертиза: подписи в карточке инструктажа — чужие</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Подпись в карточке — не работника (фальсификация после/для спора о НС)</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Фальсификация фиксации инструктажа для возложения вины на работника</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>За работника: ~1,3 млн ₽ морального вреда; акт Н-1 частично отменён</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Работник</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Поддельная подпись → нет надлежащего инструктажа → вина работника в НС отсутствует</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>НС: подделка подписи</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>https://jurisdikciya.ru/delo/52RS0004-01-2024-000600-19/</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>Общая + НС; файл пользователя</t>
         </is>
       </c>
     </row>
     <row r="19" ht="72" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Ваше</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Постановление 8 ААС от 23.04.2026 № 08АП-10045/25</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>8 арбитражный апелляционный суд</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Инструктаж до ТД / приёма</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Вводный и первичный инструктажи за несколько дней до заключения ТД</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Подпись/инструктаж ДО трудового договора, но ДО допуска к работе</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Прокуратура: инструктаж только для работников; на момент инструктажа лицо ещё не работник</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Работодатель выиграл (представление частично отменено)</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Работодатель</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Ранний инструктаж допустим, если до допуска и претензий к качеству нет</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>До ТД: суд vs разъяснения Роструда</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>https://www.garant.ru/news/2087655/</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Общая практика; файл пользователя</t>
         </is>
@@ -2026,12 +2121,12 @@
           <t>Инструктаж раньше даты приёма / ТД</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>08АП-10045/25 → допустимо до допуска</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Онлайнинспекция / Роструд → нельзя до ТД</t>
         </is>
@@ -2053,12 +2148,12 @@
           <t>Принят, допущен, инструктаж оформлен позже или не оформлен</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>12-183/19 → штраф</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>33а-6948/2024 → причина НС — отсутствие подготовки</t>
         </is>
@@ -2080,12 +2175,12 @@
           <t>Спор о вине при производственной травме</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>33-7199/14, 33а-6948/2024 → нет подписи/обучения → против работодателя</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Ульяновск (Хасанов) → журналы есть → отказ в моральном вреде</t>
         </is>
@@ -2107,12 +2202,12 @@
           <t>После НС ключевой объект — подпись в карточке инструктажа</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>2-17/2025 → подпись чужая → 1,3 млн ₽, акт Н-1 частично отменён</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>«Глазковы» → экспертизы противоречат → зависит от повторной экспертизы</t>
         </is>
@@ -2134,12 +2229,12 @@
           <t>После смертельного НС в журналах появляются подписи об инструктаже</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>ООО «Зерновая компания» (2023) → подписи задним числом → уголовное дело</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>ООО «Новый мир» (2013) / 2-17/2025 → подделка доказана судом/экспертизой</t>
         </is>
@@ -2161,12 +2256,12 @@
           <t>Журнал/карточка существуют, но не подтверждают реальное обучение</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>83-АД17-2 → нереальные даты</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>16-1837/2025 → неполные реквизиты журнала</t>
         </is>
@@ -2188,12 +2283,12 @@
           <t>Нет подписей в журнале инструктажей</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>12-460/2016 → для дистанционщиков штраф отменён</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>84-АД17-1 / 33-2135/2012 → для обычных / при очном ЛНА — строго</t>
         </is>
@@ -2215,12 +2310,12 @@
           <t>Когда должен быть инструктаж относительно допуска</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>08АП-10045/25 → можно раньше ТД, если до допуска</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>16-3241/2020 + 12-183/19 → критичен факт допуска без обучения</t>
         </is>
@@ -2286,332 +2381,332 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Особые категории работников</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9" t="n">
+      <c r="C2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>НС: подделка подписей в журналах инструктажа</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9" t="n">
+      <c r="B3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>НС: нет подписи в журнале → моральный вред</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="9" t="n">
+      <c r="B4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Инструктаж / обучение не проводились</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9" t="n">
+      <c r="B5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Формальность дат / документов</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="B6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>НС: не проходил инструктаж → моральный вред</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="n">
+      <c r="B7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Инструктаж после приёма / с опозданием</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="C8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>НС: спор о подлинности подписи после гибели</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9" t="n">
+      <c r="B9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>НС: подписи в журнале есть → вина работника</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="B10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>НС: подписи в журналах задним числом после гибели</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="B11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>НС: нет обучения/инструктажа как причина</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9" t="n">
+      <c r="B12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Инструктаж до ТД / приёма</t>
         </is>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
+      <c r="C13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>НС: анализ журнала/карточки</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9" t="n">
+      <c r="B14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Ошибки оформления журнала</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9" t="n">
+      <c r="B15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>НС: подделка подписи в карточке инструктажа</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9" t="n">
+      <c r="B16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
     </row>
